--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486357_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486357_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.7273</v>
+        <v>10.0452</v>
       </c>
       <c r="E2" t="n">
-        <v>8.9901</v>
+        <v>8.4314</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7372</v>
+        <v>1.6139</v>
       </c>
       <c r="G2" t="n">
         <v>6.8265</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9008</v>
+        <v>0.2187</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1202</v>
+        <v>-0.4386</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7806</v>
+        <v>0.6573</v>
       </c>
       <c r="V2" t="n">
         <v>1.695</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8016</v>
+        <v>5.3711</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0819</v>
+        <v>5.3739</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2803</v>
+        <v>-0.0029</v>
       </c>
       <c r="G3" t="n">
         <v>2.7727</v>
@@ -688,13 +688,13 @@
         <v>1.5225</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1886</v>
+        <v>-0.6192</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9589</v>
+        <v>-0.6669</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2297</v>
+        <v>0.0478</v>
       </c>
       <c r="V3" t="n">
         <v>1.695</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8492</v>
+        <v>2.9725</v>
       </c>
       <c r="E4" t="n">
         <v>3.408</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5589</v>
+        <v>-0.4356</v>
       </c>
       <c r="G4" t="n">
         <v>4.1667</v>
@@ -766,13 +766,13 @@
         <v>1.5225</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0103</v>
+        <v>0.113</v>
       </c>
       <c r="T4" t="n">
         <v>-0.4194</v>
       </c>
       <c r="U4" t="n">
-        <v>0.409</v>
+        <v>0.5323</v>
       </c>
       <c r="V4" t="n">
         <v>1.5204</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3762</v>
+        <v>2.091</v>
       </c>
       <c r="E5" t="n">
-        <v>1.0952</v>
+        <v>0.8716</v>
       </c>
       <c r="F5" t="n">
-        <v>1.281</v>
+        <v>1.2194</v>
       </c>
       <c r="G5" t="n">
         <v>2.3608</v>
@@ -844,13 +844,13 @@
         <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4504</v>
+        <v>0.1652</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1971</v>
+        <v>-0.0264</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2533</v>
+        <v>0.1917</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0277</v>
+        <v>1.178</v>
       </c>
       <c r="E6" t="n">
-        <v>1.019</v>
+        <v>1.3543</v>
       </c>
       <c r="F6" t="n">
-        <v>0.008699999999999999</v>
+        <v>-0.1762</v>
       </c>
       <c r="G6" t="n">
         <v>0.7798</v>
@@ -922,13 +922,13 @@
         <v>1.0875</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.6869</v>
+        <v>-0.5366</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9589</v>
+        <v>-0.6237</v>
       </c>
       <c r="U6" t="n">
-        <v>0.272</v>
+        <v>0.0871</v>
       </c>
       <c r="V6" t="n">
         <v>0.9347</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5796</v>
+        <v>0.2328</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0074</v>
+        <v>-0.2309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.587</v>
+        <v>0.4637</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9476</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3973</v>
+        <v>0.0505</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.2319</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4057</v>
+        <v>0.2824</v>
       </c>
       <c r="V7" t="n">
         <v>1.13</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0712</v>
+        <v>-0.9718</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5383</v>
+        <v>-0.4698</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.502</v>
       </c>
       <c r="G8" t="n">
         <v>0.9584</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07199999999999999</v>
+        <v>0.0273</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.274</v>
+        <v>-0.2055</v>
       </c>
       <c r="U8" t="n">
-        <v>0.202</v>
+        <v>0.2328</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2446</v>
+        <v>-2.8293</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1388</v>
+        <v>-0.8468</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.1058</v>
+        <v>-1.9825</v>
       </c>
       <c r="G9" t="n">
         <v>-4.6845</v>
@@ -1156,13 +1156,13 @@
         <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7999000000000001</v>
+        <v>-0.3845</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6165</v>
+        <v>-0.3245</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1834</v>
+        <v>-0.0601</v>
       </c>
       <c r="V9" t="n">
         <v>0.9347</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3488</v>
+        <v>-3.3728</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.681</v>
+        <v>-0.6125</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6678</v>
+        <v>-2.7602</v>
       </c>
       <c r="G10" t="n">
         <v>-0.9499</v>
@@ -1234,13 +1234,13 @@
         <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2912</v>
+        <v>-0.3151</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.274</v>
+        <v>-0.2055</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0172</v>
+        <v>-0.1097</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8902</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.4568</v>
+        <v>-4.3258</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.7593</v>
+        <v>-2.5358</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6975</v>
+        <v>-1.7899</v>
       </c>
       <c r="G11" t="n">
         <v>-3.6197</v>
@@ -1312,13 +1312,13 @@
         <v>0.87</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5772</v>
+        <v>-0.4461</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.822</v>
+        <v>-0.5984</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2448</v>
+        <v>0.1523</v>
       </c>
       <c r="V11" t="n">
         <v>-1.13</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7131</v>
+        <v>-4.5213</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.7839</v>
+        <v>-3.7154</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9292</v>
+        <v>-0.8058999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0178</v>
@@ -1390,13 +1390,13 @@
         <v>0.435</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4778</v>
+        <v>-0.286</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4795</v>
+        <v>-0.411</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0017</v>
+        <v>0.125</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5649999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.527099999999998</v>
+        <v>5.869600000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>10.6855</v>
+        <v>11.028</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.158399999999999</v>
+        <v>-5.1582</v>
       </c>
       <c r="G13" t="n">
         <v>4.645400000000002</v>
@@ -1468,13 +1468,13 @@
         <v>10.875</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.355399999999999</v>
+        <v>-2.0128</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.4943</v>
+        <v>-4.1518</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1388</v>
+        <v>2.1389</v>
       </c>
       <c r="V13" t="n">
         <v>4.3246</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.6007</v>
+        <v>6.1923</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5587</v>
+        <v>6.3352</v>
       </c>
       <c r="F14" t="n">
-        <v>0.042</v>
+        <v>-0.1429</v>
       </c>
       <c r="G14" t="n">
         <v>5.1209</v>
@@ -1546,13 +1546,13 @@
         <v>2.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6973</v>
+        <v>1.2888</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6802</v>
+        <v>0.4567</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0171</v>
+        <v>0.8322000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6671</v>
+        <v>2.6883</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3543</v>
+        <v>2.6838</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3128</v>
+        <v>0.0046</v>
       </c>
       <c r="G15" t="n">
         <v>0.199</v>
@@ -1624,13 +1624,13 @@
         <v>1.5225</v>
       </c>
       <c r="S15" t="n">
-        <v>2.1631</v>
+        <v>1.1843</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8857</v>
+        <v>0.2151</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2774</v>
+        <v>0.9692</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4981</v>
+        <v>-0.3633</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7837</v>
+        <v>1.6719</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.2818</v>
+        <v>-2.0352</v>
       </c>
       <c r="G17" t="n">
         <v>-0.5051</v>
@@ -1780,13 +1780,13 @@
         <v>1.5225</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2105</v>
+        <v>-0.0757</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2704</v>
+        <v>-0.3821</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0598</v>
+        <v>0.3064</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.0744</v>
+        <v>-1.3247</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3545</v>
+        <v>-0.0193</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7198</v>
+        <v>-1.3055</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9348</v>
@@ -1858,13 +1858,13 @@
         <v>1.9576</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1405</v>
+        <v>0.8902</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4638</v>
+        <v>-0.1286</v>
       </c>
       <c r="U18" t="n">
-        <v>1.6044</v>
+        <v>1.0187</v>
       </c>
       <c r="V18" t="n">
         <v>-3.0202</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9088</v>
+        <v>-1.8164</v>
       </c>
       <c r="E19" t="n">
         <v>-1.0875</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.8213</v>
+        <v>-0.7288</v>
       </c>
       <c r="G19" t="n">
         <v>-1.628</v>
@@ -1936,13 +1936,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2808</v>
+        <v>-0.1884</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3425</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0616</v>
+        <v>0.1541</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.1566</v>
+        <v>-2.014</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0347</v>
+        <v>1.1464</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1912</v>
+        <v>-3.1604</v>
       </c>
       <c r="G20" t="n">
         <v>-2.1224</v>
@@ -2014,13 +2014,13 @@
         <v>0.6525</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8819</v>
+        <v>-0.7393</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8663999999999999</v>
+        <v>-0.7547</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0155</v>
+        <v>0.0153</v>
       </c>
       <c r="V20" t="n">
         <v>0.1952</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1634</v>
+        <v>-2.5391</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1309</v>
+        <v>-2.9074</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0324</v>
+        <v>0.3683</v>
       </c>
       <c r="G21" t="n">
         <v>-2.278</v>
@@ -2092,13 +2092,13 @@
         <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0292</v>
+        <v>0.6534</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3509</v>
+        <v>-0.1274</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3801</v>
+        <v>0.7808</v>
       </c>
       <c r="V21" t="n">
         <v>0.3904</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4466</v>
+        <v>-3.1885</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3618</v>
+        <v>-2.4736</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0848</v>
+        <v>-0.7149</v>
       </c>
       <c r="G22" t="n">
         <v>-0.551</v>
@@ -2170,13 +2170,13 @@
         <v>1.0875</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4828</v>
+        <v>-0.2247</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3953</v>
+        <v>-0.5071</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08749999999999999</v>
+        <v>0.2824</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3252</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.1854</v>
+        <v>-3.8</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.824</v>
+        <v>-1.377</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.3614</v>
+        <v>-2.423</v>
       </c>
       <c r="G23" t="n">
         <v>-2.5843</v>
@@ -2248,13 +2248,13 @@
         <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8186</v>
+        <v>-0.4332</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.0154</v>
+        <v>-0.5684</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1968</v>
+        <v>0.1352</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5273</v>
+        <v>-5.527199999999997</v>
       </c>
       <c r="E24" t="n">
-        <v>5.1584</v>
+        <v>5.158200000000002</v>
       </c>
       <c r="F24" t="n">
-        <v>-10.6854</v>
+        <v>-10.6853</v>
       </c>
       <c r="G24" t="n">
         <v>-4.645499999999999</v>
@@ -2326,13 +2326,13 @@
         <v>11.9628</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3555</v>
+        <v>2.3554</v>
       </c>
       <c r="T24" t="n">
-        <v>-2.1388</v>
+        <v>-2.139</v>
       </c>
       <c r="U24" t="n">
-        <v>4.494199999999999</v>
+        <v>4.4943</v>
       </c>
       <c r="V24" t="n">
         <v>-4.3248</v>
